--- a/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/practice_start.xlsx
+++ b/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/practice_start.xlsx
@@ -457,8 +457,8 @@
     <col width="13.5" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="16.5" customWidth="1" min="5" max="5"/>
-    <col width="15.5" customWidth="1" min="6" max="6"/>
+    <col width="19.5" customWidth="1" min="5" max="5"/>
+    <col width="14.5" customWidth="1" min="6" max="6"/>
     <col width="22.5" customWidth="1" min="7" max="7"/>
     <col width="12.5" customWidth="1" min="8" max="8"/>
     <col width="10.5" customWidth="1" min="9" max="9"/>
@@ -536,12 +536,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -580,12 +580,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -624,12 +624,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -668,12 +668,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -976,12 +976,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1196,12 +1196,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sofia Lopez</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2428,12 +2428,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3440,12 +3440,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3748,12 +3748,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4364,12 +4364,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
